--- a/src/Reports/ExportTemplBudExcel.xlsx
+++ b/src/Reports/ExportTemplBudExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XH133LP\Documents\AL\Data Schema-1\src\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE21147-5E6B-49DC-9E78-F319456F9462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169F72DB-686E-4823-BEBE-6EE28A166F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla" sheetId="5" r:id="rId1"/>
@@ -316,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -339,6 +339,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -376,10 +383,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1055,9 +1063,9 @@
     <col min="4" max="4" width="22.54296875" customWidth="1"/>
     <col min="5" max="5" width="21.36328125" customWidth="1"/>
     <col min="6" max="6" width="22.90625" customWidth="1"/>
-    <col min="7" max="7" width="21.453125" customWidth="1"/>
-    <col min="8" max="8" width="19.08984375" customWidth="1"/>
-    <col min="9" max="9" width="17.7265625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" customWidth="1"/>
+    <col min="9" max="9" width="5.81640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1093,7 +1101,7 @@
         <f t="array" ref="H1">Data[Observaciones]</f>
         <v/>
       </c>
-      <c r="I1" t="str" cm="1">
+      <c r="I1" s="3" t="str" cm="1">
         <f t="array" ref="I1">Data[RowStyle]</f>
         <v/>
       </c>
